--- a/tools/importer/reports/import-neuwagen-finder.report.xlsx
+++ b/tools/importer/reports/import-neuwagen-finder.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="216">
   <si>
     <t>_reportFile</t>
   </si>
@@ -102,6 +102,30 @@
     <t>https://www.audi.de/de/neuwagen/?excat-fragment=model-filter</t>
   </si>
   <si>
+    <t>language-masters/de.report.json</t>
+  </si>
+  <si>
+    <t>["hero-video","carline-slider","carousel-cards","cards-image-overlay","cards-teaser"]</t>
+  </si>
+  <si>
+    <t>{"9x16_Leasingangebote_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:cedff9d8-f4ae-413a-aae8-0f081db8260c/original/as/9x16_Leasingangebote_01.jpg","cards/audi-a2-e-tron.png":"https://mediaservice.audi.com/media/fast/v3_x2TW4gbdRSH_37Zdre57syy0006TZadSVhH0k4uZjeVgCkqVKFWe_PykE6S2c3UTTZMJjFVoVgURFsQqfUGWltB0K0ofbBSKaLimyIoKEXQ9klwRanQegFx4svHOYfzO_w4nLP2q9jQdwUP71z7Y_OfGyf2_YQQw64QgZ0i0O0s3ySEaLLJaVvL9nY_3zxr5bL20Mtag-72vJlfyFb3F3LDbM7cnbVWVrLVfEyM-xqxwVci-xiL-IiqPiaOif85mnlqhDdHOfmA3z30gwdHOhGd6rsrXcu12ttcu9dd7fScgS3N22WrbOVz5aJdr9cXF0v1smUu1QvlJdMsFXNmwS6Um43GrQ3ZH_GOCDTtvpg8XK_1nKZdyxVNc1gyc2Jjq9GxHFeMjZxjPMvWK0w_j7IX5SWU8xhPEf-XRJXESRJrJC5gHEB9ldQ5UhdJfY3xHHPX0cA4jnYY7TfSf5N5gUwdcTvGLsIu4deIvE1MIbbAzJNs-QK1g1ondRvpXaRvIOKIB5A-Rp5i-iRKkcQSqow6ix5AN9Avk_6A4DjBtwiXiBYxHkc6iryKfAbjPuKPEL-GHkN_A_1L0iVCdxO6jrSOcpbIe0QuIe1AqiF9hvQV8r3IfaZPEP8IdTfzt5C8TPIGyX9ITZCaJDWL8RBzv6Al0E6heWiX0Pej_05aJq2T_pHIaSLniXWY_JCbTxNbZKbHzCsYh4ifIXGQxEUS36A2SH5C8lNi3zP_NMozGMeYu0L6c8Q44ijGnWy6SvB-gm2CrxM8S_AHQocIHSF0lXCYsO__BJFviUaI3kP0INEu0ePEqhjvE3-RLV3Ud0ntIDVg7i-0eaS7kCPE_c0cwdiK9jPRdWLrSGNIL2M8gfIYynf-aSzbnYHjrnbadser7PX6TWc186jT9FqVolkuZVq2s9zyKgVzIZ-xVrotq-K5fTvTsNq2a1WqB_bk76hVa4WaaZoZq-N_hef4B1rJtG3PalqeNbDdnl-p5KcCfvN_25OpJF0DAAA.png","cards/audi-a3.png":"https://mediaservice.audi.com/media/fast/v3_x2TX2hbdRTHf37Sbm16c9N7S--SNCSSe28oldibP23aaXQd4sMQlc46RCH7tbltU5o_pjcxVQRfxL1MfHD-mYhSB0O3iaKIsLHNfwMZm4IPSl8se1FZVXDgJiJ668uHcw7ne87hcM7pX0VvuyV4fP_pG3tu7ep7ZAshuk0hAsdEoFlfuk0IUaG_WpNL7rjv77FlPuN2vYzsNMdzTq6YkfmmzDxQzczM5ae6mal1JyNXV8Nity8Uvb6cuI-efh_qAR99afE_dwpv7OCrHZ9swM_u-sZjOzqhDrVbq03ZkrU7W-5as1Ffq3ZcbXSqMF-UE9Pu4qKzODE1n5XTrnQL85N5N5vP5hcmnEJ-olJcmNf9El-KQMVti8GV-fJateKWswXH6U46WbFrar0j6wuiZ2d8kreIX2P4JYyDGB9gfETkBtG7iY0RmyH2MrH3iH3KyL_Ej5M8Q_IsyW9JbZL6A1NgrmD-jv0P6XHSDyL2ETyP0iJ0EvVewgaRZ4mcYeQS8QZxSfwoY1Wsq9g3EVFEDn-92jm0y-igDzH8NsZdxBaJ61hjWJvYHxLsJXgCpYhyD2oBzUNfRT-FYRCtEL1M9Ddi21hhrBRWAauM9RbWFez9DBxg4E-Uj9Hvx3gH4xKhrwl9grqBthetjPYF2lX0NPok-kPoHsNHiZ4lPsvoHSQ2Sdwk8TfJHpKDJG8ndR0zgvkKpod5DmsO6ydsHdvC_hHlEMoJQq8S-oVwnfAbDM4xuMXYBcxpIh6R40S-Yeww0Q1ifpcFEhdJfI55AUUj_ANDRYaXMY5gXCTyBJEVIs-TrJHawi5jP4n9OvZniN2IZ-jfJjhLsEbwOgOHGVhn4BqKgvIuyvuEXiT0Heoh1Abqc6gvEJ4h7LNL9E1GmsRPkThPci_JDqm_MEfR9hGdJbpOXMG8gvkz9hGUAMoI6jHUbcLbaH1or2E8jfG9f2hLbr1TbTXqNbfulQ567Uq1kX6qWvGWSwVnejK97FaXlr1S3inm0nK1uSxLXqvtphdkzW3J0syjD-fuK8-U82XHcdKy7j-aV_XPvZSuuZ6sSE923NaaHynlhgJ-8n8dZGj4sAMAAA.png","cards/audi-a5.png":"https://mediaservice.audi.com/media/fast/v3_x2TXWgcVRiGT59Nmmazs5uZkMnudNyVndklpKyd_cmmqa4YlVx40YppKuLF9iQz7m6S3Syb2TSSXnhT9cYfsPhTlUJtb7QopVKsLf5bCmJBvbCooO2VYkRQaSoiOPHiPJz38L3fdw6858xvorfbETx675k_R25t33HgJ4RYawsROi5C7VZtmxDCpb_RlDVvd6BHbDme89b8nFxt7y44hYlcoKdmS85abs_herAWc3JpKSb6Ap_oDdzbTgXoGQwQfS3Ajrz4n1t9n9zClS2NEwqq14LNI1s-ER3qdpbasiObd3S8lfZya6Wx6qmj5cmSnHdLXn6uLKXn7ilPFCeLjisdKR23UJ4syrzjlvNlLWhxWYRcrysGF-aqKw3Xq-ZLjrNWdvJi-2PdgmzXRM_W7UmPc9t1hp9Hn0E_R_wWibswxjCmMI5hvInxHqkcqdOkLpL6ivQ10n9gCawFrN_JjpAtkl1E3ENYIXyU8AdEOsR04uvE32HnZcwW5hzmM4w1SN2J_QL2VTKbiALqJbQhho-hT6AHE2uYGuYodgh7DPs7MmcJ9xE-ReRuoiVUH62F9jn6LhKLJL4g8RfGBlY_dgw7jV3FPkEmz8ADDNwk8i5aHG0a_Q2Ut1EuoJxHuYm6F7WKKlE_Rb2KlkUbR9uP1iVxEXMf5hFGd5H8nuQmyX9I_kuqh9Qg6Sukf8UysF7E8rEuYc9ib5LRyNhk9pP5kchJlJdQzqH8QqxF7FUGZxm8gLGONUl8hfhxxg6ROInxMMZ5jPcx50l-RPITrA-JaMSuMXSD4Tr60-gfM_Ic8QXiR8lUybxC5rMgoog-xBH6NwjfR3iGcJPwDwwcYmCdgRtEIkSC9z6L8g1RhahJ9AliU8QOEHuK2An0aRKvY1xnZxvzLcyvSe0ldZDUKum_sUZRp9EUEg-ReBwzgvUl1s9EQkRuJ7pBbAO1F_Vl9HX0b4O41bzWaqOz3Gp6Lb8y43fdxnL2cMP165WSM1nO1r1Gre5Xis5EISuX2nVZ8TtdLzsvm15HVqYOPli4vzpVLVYdx8nKVvDb_EYQ-kq26fnSlb5c9TorwUmlMBQKiv8DYOrdkbUDAAA.png","cards/audi-a6.png":"https://mediaservice.audi.com/media/fast/H4sIAAAAAAAA_1vzloG1tIiBOTrayfuvpGh6-m1zJgaGigIGBgZGoDhTtNOaz-I_2DhCHsCEtzEwF-SlMwJZKUycmbmJ6an6QD4_I3taTmV-aUkxO0grz9Wu1QZ56rnMhy1ePSvpKdrvVd7gyMAK1MXYByRYGIEE3z8gwWHDACZB5oEN3QniMxkyMzCwVgAZkQwgwMdXWpRTkFiUmKtXnplSkiGoYUAkEGZ3cQ1x9PQJBgCLqOBV6QAAAA.png","cards/audi-a6-e-tron.png":"https://mediaservice.audi.com/media/fast/v3_x2TXWgcBRDHN79rPrrZu81uyOb2ut5pdveMkbN730nlxCsSS5FWiaaID9dNbnN3MXc5LntnpBVUKPiiKIIWoURK6YMGixSK1KKtXxQFH-xLLT60FaFiRFBoFVHc-PJjZpj5DzPMbP4q9Hc7As_s3fxj_M-BoSevIwjrbUEInRBC7VatTxCEKjsbTbfm7Q788Sm3kPLW_ZTba-_OOJliqlzw_M5qq9xzW36q_FQ-vZ6azZdT7sqKLAwG1UJ_oNF3IMCOwQCRcwGGDgn_c1v9hW1c2vZxQkH2emA8vV0nREa7nZW223GbD3S8tfZqa63R85TJ6aWiU83PLC1OZ2fcpXRmKVtYKGa8fCGbzhRzmYVc2ssWpxc9NZD4UghVva4wsrxQWWtUvUo65zjrBSctDNTqeXfBFXZsz8A9j3HXDcZeR5tDexvtLLqI_i-xMrE3iG0S-wjjOIkUifdIfEziChNXmbiNCaaIuYz5G8kEyf0IDyOGEMOIx5A6SBvIGtEjRM-w6yuMFsYCxqtMNUg8iPUm9j7sOwgZlAuoo4ydQSuiBX1rGCrGJMY-rBDWFNY17A8RBxFPId2LVEB6iEgOdRX1AloI_Vn0b9B_x5KxbKw8VgVrA-tr7BzDexm-jbKFGkWdRTtN-APC5wmfI3ISRULZg1JBcVE-R_kW9SBqF_0ixgGMo0zeT_wa8TvE_yb-D4khEiNMXGbiF8wY5luYPuYnWPNYt7BVbB17P_ZB7OtIpwi_S_gs4Z-RW4y8jDlDdI3oO0wdRj9J7BCx8xhV4heJf0b8J8xPkRTkq0yFGKujvYJ2ifE-ostEj2FXsL9AGEQ4ys6biI8iziE2EX9g-DDDRxi-iSQhTSMFM75G-AqRMJEXkcvI88gvIW9w32W0WfQTxG6wq43xPsZ3JPaQ6DHxF-YkyiyqjP4E-vMYEuYtpAGku4lsIW-h9KMcRwlW9yPa98Gt1bxWrxF8QtNr-aU5v1ttrCafa1T9einnzBSSda9Rq_ulrFPMJN2Vdt0t-Z2ul1x0m17HLZXnH888UilXshXHcZJuK3g4vxFcfCnZ9Hy36vpuz-usBZFSZjQUJP8HmeY5vLgDAAA.png","cards/audi-q3.png":"https://mediaservice.audi.com/media/fast/v3_x2TW2gcdRSH__22adrN7mxmQqY7kzEjmd0xiayZvWQ3qSwYKRH6ULUxVVHYTrKzyYbsZt3Mxpj6oILYlxYfWqsVaUl9sValREOhRaXRIgoqIiit4OXJS0TESxUfdOLLxzmH8zsXOOf8z6Kt1RQ8dOf533b_tWPnfd8gxHJDiNCqCDXqM9uEEGV2VWvujDcU-LvtR7Ipb9lPuUuNoYyTKaTGJrPZfGo8m0658_Ope7MTkwdT---KifZAKdoC_bbrAUI_BZBCAXY2xf_cqry6hdNbPk4oyF4OjAe3dELqajXnG27Trd3W9BYbC_XF6pIn9-enC-VCrpAv5Nx0biSbH3GGR0eGc9NuJjc65Xjl0dzUcMXzRpSgxAciVPZaonNuqrRYLXuldM5xlvNOWuyozE25KzNi-9b8DJzjpgrdz6JOoJ5EXWPgJNpb6IPoY-jH0c-hX6TnX4xTmCnM1zAvYX5K3zX6_sASWBWsX7B17CHsfYg7CEcJv02kibSXmEr8SeJv0HMVo44xhXGUwSrm7SQ-IXkDoSEyiAeQLyN_iNKG0kX3cdQCegVDwegnESIxSOIayQuE2wm_TKSAlENeQamjrKOqaGW0j9B-JxEjsULiNIk1kmk69tHxJ5E3UcZRz6JeJfo60StE15FWkdPIe5BLyBeRN5A_RrFR8ih3o7ToPop2CWM_xmH6b6X3Or036P0HcztmJ-bN9P2KpWM9h-VjXcZ6n8QkAxdIKiQ1kl8TPUN0jegPxOrEXqRzks4NBs4QGyG-SPwUg4fQVtHvR19HD3qV6b2C9Q6xL1G-petHumdRj6C-y8AG8TniT2NWMJ8iWSL5Asn3EO2Ix9m1SfgA4Rrh04TPEv6KjkN0HKbjOyIRIq8QCbY-RvRzpCjSw0g-0hNIx4iNEXsG7SV6GhivYnyGuQdzib6_sfqRx1GiaAfQHsOIYH1P8giRENIJpE1im8htyM9zywnUL4Kjm_HqS9XmQr3m1f3ihN8qVxfsR6tlf7aYc0bz9qxXnZn1i1mnkLHd-casW_SbLc-edmte0y2OHbwns7c0VsqWHMex3XrwdX41OP2iXfN8t-z67pLXXAwixUxXKEj-D7iZcKa9AwAA.png","cards/audi-q4-e-tron.png":"https://mediaservice.audi.com/media/fast/v3_x2TW4gbZRiG_z5xu9scJjuzbHYnO2ZKJgnr2Ngkm002lYCpB2hBtK0tniBOkkk2ZZNNZydxoVrwSlEKVfCMrIjsha2HpSCFSlmseCMekAWlN9q9EMWKoNB6QHHizcP3_nzvx8fP-537RYz0HcEj-8_9PvXHzrEHvkeI1Z4QPkf4et3WDiFEg13tjtWy93p6KnUin7ZX3bQ16O3NZXLF9CFPu85yN105OpctpBdKVtpaWgqLUc8pRjz_jjc8-NY8SHs8jJXF_xxOfn6ItaEm6_O6V73ioaFPSBN9Z6lnOVbnNsde6S13V9oDW57N1edzuVKzUFtoWtZ8bq5YLxXtUq1uFbJ2MZ9tFoqFYqlWyCjeiAvC17D7Yvx4rbrSbtjVbD6TWS1ksmJnM9-yFjvipuH-7L4TbZvJM0SOEHmZyHlUGfVfohWizxJ9h-gFzGNor6G_i34R_SviV4hfxwBDwjiO8SvJv0i9QKqOuAfzAP4QQYfg64TWCUcIF5l-iun3mfkUrYtWQ7-dxJckD5C8gVAROcSDyB-hTDC5QSRPtImmoM2S8JEwSVwhuYF_FP_bSHnMe5G7KD2UdcxDqA3Uz1B_IxEmMU9ijcTnJAsE9hO4TmSd0CWkt5D3IVeRLeTLyF-g3IfiMnkadRPtMNqTaJeZvZXYNrEbxP4m9g_6GPo4-m70M5gPE_8ZI4rxEoaLcYnEUW7ZIKmQVEl-R-hNQucJ_US4y_iHRE8SXmB6wPSrqOtELxLdQmsQ2yT2McYmQYXwtyhXMfcQeYbIJlNb6KeIXyVZJfkJYhTxBObd7NrGfxj_CQI-Ao8ROElgm2AQ8yDB9widJrSFFEJ6FKmH9BzhCuYHhJ9GfZGZHtpZtK_R96H3iP-JMYt8B0oI1fu6U5g3Y_xIcAbpGuFryCPIryD_QOQbL0Qtuztoe-nu2F23fMTtN9rLqcfbDXexnM-UCqlFu91adMtzmWIuZS31Fq2y6_TtVN3q2I5Vrhy7P3dXtVKdq2YymZTV9a7IbXtRLqc6tms1LNca2M6K91LOTfi85v8AtYt2u40DAAA.png","cards/audi-q5.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGE4wMBfkpTMCWSlMnJm5iemp-kC-OH9aTmV-aUmxvpGBkbluoSk_IztUhB2olJGHYTn3jH02vseip-3cZHh4ynHf3yc3_GdgBZrDOB1IMJ8FEvwMQIJjPYQE2VADIiaC-EyGzAwMrBVARiQDCPDxlRblFCQWJebqpaQmlaYLahgQCYTZXVxDHD19ggHJwayh4wAAAA.png","cards/audi-q6-e-tron.png":"https://mediaservice.audi.com/media/fast/v3_x2Tb2gbZRzHn32ytV1ySXpXd81lZzJyd7FW4i5Z_qyTiJlSRcQpdRPxRXZpLmlqk2bJpXbUF74ZE2GgKDIEmXT6RosiA5Epbk6RoSDi3mjxxTpRJlYEhU0RxatvPjzfH7_v73l-8H3WfhU7Bj3BkwfX_hj_c2jksasIsdwVInBSBLqd5jYhRJ2drbbTdPf6ejztFDPuspdxlrp7c3aulDnma6-32MlUDuezy5lGoZ9xFhaiYth3ih2-f9uQj8CGj8hbPkZ-Ev9za_LxLTy_pbEDfveyf3hiyyciY4PeQtfpOe07e26_u9jpt5ZceaLounat6GYbDddxC7PZUqM-lSvUCo1sPZfN5gu1UqHg5PY3FH_EBRGouwMxOl-r9lt1t5rN2_Zy0c6KoWaj5mQdsX3r_ey5l1s32PUC6gzqObQQ2r_EK8RfJL5G_AP00yQzJN8k-SHJK6TWSd3AACOIMY_xG-kk6YcQ9xAMEAwTPIHUQzpDVCW2Quxddn-O3kGvoZ9iskXyLsyXML_GegDrJiKH_BHKGLteRi2h-lc30RX0CcwA5iTmOtZ7BIcJvoF0G1IR6W4ieZQ2ynnUANpTaF-i_Y4ZxUxhVjHPYH6BlSd0kNAN5E2UGMo06lnC7xC-RPh95APIVWQH-VPkr1AOoQzQLqI_jL7CxB0k1kncJPE3iX9IjpAcJXWZ1C8YcYxXMDyMjzEPY17HUrA0rAexDmFdRVol_Drhc4R_Jtph9BjGFLE-sVeZPIq2Svxx4ufR6yQukrhE4keMC0gK0W-5ZRb1OdRPGB8jNk_sBFYV6zPEMOIZdl4jeD_BGYJtgt8TOkpohdA1JAlpP5K_2inCV4iEiehEniVaIXqE6Eluv4w6jfYa8Q12d9HfRv-G5AFSf2FMIE-jhNEeRTuOLmFcRxpC2kNkk-gm8nbk08iryD-gfucnq-l2llp-5NtuxyvPeIN6azH9dKvuzZXz9lQxPee2mnNeeZ9dyqWdhe6cU_Z6Azc967TdnlOuHHkkd1-1Ut1XtW077XT8r-W1_HyX023Xc-qO5yy5vb5fKefGAn7zf7KBWguiAwAA.png","cards/audi-q7.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGE4wMBfkpTMCWSlMnJm5iemp-kC-OH9aTmV-aUmxvpGBkbluoTk_IztUhB2olJGH4Wdzv6Sh50eFh52zTiU5L5xc0nYhn4EVaA6jOJBgjgASfEeABEcnA5gE2ZABIvJBfCZjZgYG1gogI5IBBPj4SotyChKLEnP1UlKTStMFNQyIBMLsLq4hjp4-wQBRTCXI4wAAAA.png","cards/audi-q8.png":"https://mediaservice.audi.com/media/fast/v3_x2TT2gcdRiGf3m2SdvNzG5m4k53N0MGd2a2IZJmdpPmn11pahERtNLWFvGwmWRnk02zk83ubJraKnoQvFQvxaJCe1AiaBWCImKLtBYaghiqHpSe1IuK6cWiNeSgk14evhfe7-U9fN-Vu6K1WRe8cOjKvT3_tu06_jNCLNWEiKyISM2fbhFClNhdqbrTXn-o9-gLI33eUtDnLtb6805-uG9hpOb2DVbLfe7cXFzsDP2iNdxqORAicj1E7EaIXSviAR_kbePctiYXCd1L4fD89p6IdTbrczW37lb31b1Gbd5vVBY9pWfUy40MDU9NjXiT3vDkaHl_bsDxyrncaFggP-KW97vuwECp7KhhxJqIlLym6JidLDYqJa-YG3ScpSEnJ9oGq4EzmRc7tlvz8Brd_WjH0D4lZZM6QLqX9DjpC6Q_JP0FRj_GMsZVjHWM78jcJvM35gTmX2RlsofJ-oiDSHXkZeIaiSbJl-m6he6jT6Cfp7dC5g-sd7DWse8j9hF9FOVNlGuonSQuoA2TnkXvRN-L_iRWBKsX6w52Avsk9grRVqLvI-1FGkJ6DDkgNojyNMqLqPOoqyS2SL5Hyif1Dan7pDcw2zA3seJYJlYR6zLW19iP0_4U7f8gfYb6BNoy8m3kz5HvIm-hjKEUUVyUmyjrqD2oBdQjqM-hNkmcJ7WK_gz6l_Q8QvcdurcwdmB0YNhk_sR8CzPAvIZ5A_MW1gms_7BV7BT2EewNpA-QLyL_Rtwn_i4dx-m4h5nHHCXZJH0VSSH-Ew9tkphBex3tOskxkrMkX8M4hV3GXsB-G3sN0YLYiTjH7g2ih4geJVolukr7JO1naf8VSUb6COkT5AnkN5B_ICYT04m9Qnyc-KvEL9PRQ-oS6V_oqqF_jP493V9hjGGcxFgks4nZg3KQ1FFSZ9AlzG8xf0dqQ-oitkF8A6UV5SLaWbRLaDfRfgzv7iXPX6zU5_2q5weFY0GzVJnPnq6UgpnCoDM6lJ3xKtMzQWHAGc5n3bnajFsI6k0vO-VWvbpbGD_xbP5wcbw4UHQcJ-v64bsFlfD6C9nG1HwtdJw-5Z1peAtNz5_yCvls1Qvckhu4i169EfoK-c5IGPE_puUsMswDAAA.png","cards/audi-q9.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGE4wMBfkpTMCWSlMnJm5iemp-kC-OH9aTmV-aUmxvpGBkbluoSU_IztUhB2olJGH4dPkY46s-6KbtFgT_-lEnzY4KnLkFAMryJzrQILZFUjw6wAJjnYGMAmSiQYRxSA-kxEzAwNrBZARyQACfHylRTkFiUWJuXopqUml6YIaBkQCYXYX1xBHT59gAGx0n1DjAAAA.png","cards/audi-e-tron-gt.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGE4zMBfkpTMCWSlMnJm5iemp-kC-uFBaTmV-aUmxvpGBkbluaklRfh4_IztUkB2ompGH4XjRqu9uj7VdK8UFWr2dj9dMP95Rw8AKNIpxPpBg0QISfL-ABIcHA5gEWZIJIk6C-EwWzAwMrBVARiQDCPDxlRblFCQWJebqpaQmlaYLahgQCYTZXVxDHD19ggEPp39D5gAAAA.png","cards/audi-nuvolari.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGLYwMBfkpTMCWSlMnJm5iemp-kC-uFRBUX5KaXJJSmpJYmZOsX5afooulM3PyIcqyQ7UzMjDEBjWe-dDzqpFyy9ofdnj-Hin56m76xmYGRjYGxgYWCwYQIBPuLQopyCxKDFXryi1uCA_rzizLFVQw4BIIMzu4hri6OkTDAD_J8cizwAAAA.png","cards/audi-f1.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGLYwMBfkpTMCWSlMnJm5iemp-kC-uFRBUX5KaXJJSmpJYmZOsX5afooulM3PyIcqyQ7UzMjD0CK89NsGXslvP2aeuao66f8-K6u9DgzMDAzsDQwMLBYMIMAnXFqUU5BYlJirV5RaXJCfV5xZliqoYUAkEGZ3cQ1x9PQJBgBHdTswzwAAAA.png","1x1_Q9_2026_8802_withoutCast_02.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:78620da7-9245-4f73-8052-60256fa6cb25/original/as/1x1_Q9_2026_8802_withoutCast_02.jpg","A2e_2026_9667-S.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:c59f36c7-7701-4706-bede-958032bd6e86/original/as/A2e_2026_9667-S.jpg","1x1_Q7_ae_2026_8627_02.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:8766edf6-e8a7-4d3d-a428-e2629b9ba8ef/original/as/1x1_Q7_ae_2026_8627_02.jpg","1x1_Audi-driving-experience_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:47cb8339-8b41-44a6-9013-b42a1d4c56f0/original/as/1x1_Audi-driving-experience_01.jpg","1x1_Nuvolari_2026_9606_3_to_4_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:47beff9b-7bc4-4d7d-a0e0-eddef24a7c32/original/as/1x1_Nuvolari_2026_9606_3_to_4_01.jpg","1920x1920_RSeGTp_2024_6598_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:5aadf297-9332-40aa-ba6b-3eb9c4e8a7dc/original/as/1920x1920_RSeGTp_2024_6598_01.jpg","1920x1920_Gebrauchtwagen_q8_2023_5482-30724177_02.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:3ff1543f-0c38-431f-b69b-38bad983eeaf/original/as/1920x1920_Gebrauchtwagen_q8_2023_5482-30724177_02.jpg","1920x1920_Q5_2024_6816_1_V4_02.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:0861f618-db68-43e0-b039-f658d1e08f7f/original/as/1920x1920_Q5_2024_6816_1_V4_02.jpg","1920x1920_Probefahrt_Q4e_2026_8409_DE_02.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:aab09321-0c1e-4fa0-9929-b51fe7f1140b/original/as/1920x1920_Probefahrt_Q4e_2026_8409_DE_02.jpg","1920x1920_exclusive_sq6_ascari_05_04.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e36deb3d-0460-4c5c-ac56-9ce8fb6ec047/original/as/1920x1920_exclusive_sq6_ascari_05_04.jpg","1920x1920_eGT_2025_7809_Cast_04.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:97c2514e-0c23-45fa-a283-9e9e8fb07177/original/as/1920x1920_eGT_2025_7809_Cast_04.jpg","9x16_A6_2026_9257_1_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:424c701a-1022-4951-9b10-19ac1ce76517/original/as/9x16_A6_2026_9257_1_01.jpg","1920x1080_VST.jpeg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:0d6cea04-7412-4955-98ec-0b9aaa34c237/original/as/1920x1080_VST.jpeg","16x9_Audi_WKR_2026_Keyvisual2_02.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:7ba429c1-3761-4f69-b612-e286dca4abfa/original/as/16x9_Audi_WKR_2026_Keyvisual2_02.jpg","16x9_as_2023_5877-32641384_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e88cfb16-2ce0-4093-90de-e462cf6de548/original/as/16x9_as_2023_5877-32641384_01.jpg","1920x1080_A223159_large.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:11aed372-f8ba-41a8-8582-fcdc7beb44b8/original/as/1920x1080_A223159_large.jpg"}</t>
+  </si>
+  <si>
+    <t>language-masters/de</t>
+  </si>
+  <si>
+    <t>home</t>
+  </si>
+  <si>
+    <t>2026-10-28T13:53:38.254Z</t>
+  </si>
+  <si>
+    <t>Modelle, Aktionen, Angebote | Audi Deutschland</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/</t>
+  </si>
+  <si>
     <t>language-masters/de/elektromobilitaet.report.json</t>
   </si>
   <si>
@@ -339,7 +363,7 @@
     <t>language-masters/de/neuwagen/a3</t>
   </si>
   <si>
-    <t>2026-10-27T20:15:58.463Z</t>
+    <t>2026-10-28T15:13:06.135Z</t>
   </si>
   <si>
     <t>https://www.audi.de/de/neuwagen/?bycarlinegroup=a3</t>
@@ -474,7 +498,7 @@
     <t>language-masters/de/neuwagen/q5</t>
   </si>
   <si>
-    <t>2026-10-27T20:16:25.980Z</t>
+    <t>2026-10-28T15:13:09.840Z</t>
   </si>
   <si>
     <t>https://www.audi.de/de/neuwagen/?bycarlinegroup=q5</t>
@@ -609,7 +633,7 @@
     <t>language-masters/de/neuwagen/q5/q5-sportback-e-hybrid</t>
   </si>
   <si>
-    <t>2026-10-27T17:22:09.364Z</t>
+    <t>2026-10-28T14:03:37.504Z</t>
   </si>
   <si>
     <t>language-masters/de/neuwagen/q5/q5-sportback.report.json</t>
@@ -618,7 +642,7 @@
     <t>language-masters/de/neuwagen/q5/q5-sportback</t>
   </si>
   <si>
-    <t>2026-10-27T17:22:04.513Z</t>
+    <t>2026-10-28T14:03:32.765Z</t>
   </si>
   <si>
     <t>language-masters/de/neuwagen/q5/q5-suv-e-hybrid.report.json</t>
@@ -627,7 +651,7 @@
     <t>language-masters/de/neuwagen/q5/q5-suv-e-hybrid</t>
   </si>
   <si>
-    <t>2026-10-27T17:22:00.558Z</t>
+    <t>2026-10-28T14:03:28.464Z</t>
   </si>
   <si>
     <t>language-masters/de/neuwagen/q5/q5-suv.report.json</t>
@@ -636,7 +660,7 @@
     <t>language-masters/de/neuwagen/q5/q5-suv</t>
   </si>
   <si>
-    <t>2026-10-27T17:21:56.358Z</t>
+    <t>2026-10-28T14:03:24.267Z</t>
   </si>
 </sst>
 </file>
@@ -1025,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="50" customWidth="1"/>
@@ -1155,10 +1179,10 @@
         <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
@@ -1170,33 +1194,33 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
       </c>
       <c r="I4" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="J4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K4" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="L4" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
@@ -1208,22 +1232,22 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="J5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K5" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="L5" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -1243,7 +1267,7 @@
         <v>15</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="s">
         <v>43</v>
@@ -1269,10 +1293,10 @@
         <v>48</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
@@ -1281,36 +1305,36 @@
         <v>15</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H7" t="s">
         <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
         <v>15</v>
@@ -1322,33 +1346,33 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H8" t="s">
         <v>17</v>
       </c>
       <c r="I8" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
         <v>15</v>
@@ -1360,33 +1384,33 @@
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H9" t="s">
         <v>17</v>
       </c>
       <c r="I9" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D10" t="s">
         <v>15</v>
@@ -1398,33 +1422,33 @@
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H10" t="s">
         <v>17</v>
       </c>
       <c r="I10" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
         <v>15</v>
@@ -1436,33 +1460,33 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
       </c>
       <c r="I11" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
         <v>15</v>
@@ -1474,33 +1498,33 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H12" t="s">
         <v>17</v>
       </c>
       <c r="I12" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
@@ -1512,33 +1536,33 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s">
         <v>17</v>
       </c>
       <c r="I13" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
         <v>15</v>
@@ -1550,33 +1574,33 @@
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H14" t="s">
         <v>17</v>
       </c>
       <c r="I14" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K14" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L14" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B15" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
@@ -1588,33 +1612,33 @@
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H15" t="s">
         <v>17</v>
       </c>
       <c r="I15" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="J15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K15" t="s">
-        <v>38</v>
+        <v>102</v>
       </c>
       <c r="L15" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
         <v>15</v>
@@ -1626,30 +1650,30 @@
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="H16" t="s">
         <v>17</v>
       </c>
       <c r="I16" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J16" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="K16" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L16" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>110</v>
+      </c>
+      <c r="B17" t="s">
         <v>105</v>
-      </c>
-      <c r="B17" t="s">
-        <v>97</v>
       </c>
       <c r="C17" t="s">
         <v>106</v>
@@ -1664,19 +1688,19 @@
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H17" t="s">
         <v>17</v>
       </c>
       <c r="I17" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J17" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="K17" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L17" t="s">
         <v>109</v>
@@ -1684,13 +1708,13 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D18" t="s">
         <v>15</v>
@@ -1702,33 +1726,33 @@
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H18" t="s">
         <v>17</v>
       </c>
       <c r="I18" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J18" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K18" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L18" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B19" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D19" t="s">
         <v>15</v>
@@ -1740,33 +1764,33 @@
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H19" t="s">
         <v>17</v>
       </c>
       <c r="I19" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J19" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="K19" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L19" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B20" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C20" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D20" t="s">
         <v>15</v>
@@ -1778,33 +1802,33 @@
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H20" t="s">
         <v>17</v>
       </c>
       <c r="I20" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J20" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K20" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L20" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B21" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C21" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D21" t="s">
         <v>15</v>
@@ -1816,33 +1840,33 @@
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H21" t="s">
         <v>17</v>
       </c>
       <c r="I21" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J21" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K21" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L21" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B22" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C22" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D22" t="s">
         <v>15</v>
@@ -1851,36 +1875,36 @@
         <v>15</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H22" t="s">
         <v>17</v>
       </c>
       <c r="I22" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J22" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K22" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L22" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B23" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C23" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D23" t="s">
         <v>15</v>
@@ -1889,36 +1913,36 @@
         <v>15</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H23" t="s">
         <v>17</v>
       </c>
       <c r="I23" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J23" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="K23" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L23" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C24" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D24" t="s">
         <v>15</v>
@@ -1930,33 +1954,33 @@
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H24" t="s">
         <v>17</v>
       </c>
       <c r="I24" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J24" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K24" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L24" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C25" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D25" t="s">
         <v>15</v>
@@ -1965,36 +1989,36 @@
         <v>15</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H25" t="s">
         <v>17</v>
       </c>
       <c r="I25" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J25" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K25" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L25" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C26" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D26" t="s">
         <v>15</v>
@@ -2003,36 +2027,36 @@
         <v>15</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H26" t="s">
         <v>17</v>
       </c>
       <c r="I26" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J26" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="K26" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L26" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C27" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D27" t="s">
         <v>15</v>
@@ -2044,33 +2068,33 @@
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H27" t="s">
         <v>17</v>
       </c>
       <c r="I27" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J27" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K27" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L27" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C28" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D28" t="s">
         <v>15</v>
@@ -2082,33 +2106,33 @@
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H28" t="s">
         <v>17</v>
       </c>
       <c r="I28" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J28" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="K28" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L28" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C29" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D29" t="s">
         <v>15</v>
@@ -2120,33 +2144,33 @@
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H29" t="s">
         <v>17</v>
       </c>
       <c r="I29" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J29" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K29" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L29" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C30" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D30" t="s">
         <v>15</v>
@@ -2158,33 +2182,33 @@
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H30" t="s">
         <v>17</v>
       </c>
       <c r="I30" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J30" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="K30" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L30" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="C31" t="s">
-        <v>42</v>
+        <v>179</v>
       </c>
       <c r="D31" t="s">
         <v>15</v>
@@ -2193,10 +2217,10 @@
         <v>15</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="H31" t="s">
         <v>17</v>
@@ -2205,24 +2229,24 @@
         <v>44</v>
       </c>
       <c r="J31" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="K31" t="s">
         <v>46</v>
       </c>
       <c r="L31" t="s">
-        <v>47</v>
+        <v>182</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D32" t="s">
         <v>15</v>
@@ -2231,36 +2255,36 @@
         <v>15</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="H32" t="s">
         <v>17</v>
       </c>
       <c r="I32" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J32" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="K32" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L32" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B33" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D33" t="s">
         <v>15</v>
@@ -2272,33 +2296,33 @@
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="H33" t="s">
         <v>17</v>
       </c>
       <c r="I33" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J33" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="K33" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B34" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D34" t="s">
         <v>15</v>
@@ -2310,33 +2334,33 @@
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="H34" t="s">
         <v>17</v>
       </c>
       <c r="I34" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J34" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="K34" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L34" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C35" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D35" t="s">
         <v>15</v>
@@ -2348,33 +2372,33 @@
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="H35" t="s">
         <v>17</v>
       </c>
       <c r="I35" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J35" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="K35" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L35" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B36" t="s">
-        <v>191</v>
+        <v>49</v>
       </c>
       <c r="C36" t="s">
-        <v>192</v>
+        <v>75</v>
       </c>
       <c r="D36" t="s">
         <v>15</v>
@@ -2383,36 +2407,36 @@
         <v>15</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H36" t="s">
         <v>17</v>
       </c>
       <c r="I36" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="J36" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="K36" t="s">
-        <v>195</v>
+        <v>78</v>
       </c>
       <c r="L36" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
+        <v>199</v>
       </c>
       <c r="C37" t="s">
-        <v>73</v>
+        <v>200</v>
       </c>
       <c r="D37" t="s">
         <v>15</v>
@@ -2421,10 +2445,10 @@
         <v>15</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="H37" t="s">
         <v>17</v>
@@ -2433,24 +2457,24 @@
         <v>44</v>
       </c>
       <c r="J37" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="K37" t="s">
-        <v>76</v>
+        <v>203</v>
       </c>
       <c r="L37" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B38" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C38" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D38" t="s">
         <v>15</v>
@@ -2462,33 +2486,33 @@
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="H38" t="s">
         <v>17</v>
       </c>
       <c r="I38" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J38" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="K38" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L38" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B39" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C39" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D39" t="s">
         <v>15</v>
@@ -2500,33 +2524,33 @@
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="H39" t="s">
         <v>17</v>
       </c>
       <c r="I39" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J39" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="K39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L39" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B40" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C40" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D40" t="s">
         <v>15</v>
@@ -2538,22 +2562,60 @@
         <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H40" t="s">
         <v>17</v>
       </c>
       <c r="I40" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J40" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="K40" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L40" t="s">
-        <v>95</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>213</v>
+      </c>
+      <c r="B41" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41" t="s">
+        <v>99</v>
+      </c>
+      <c r="D41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" t="s">
+        <v>15</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41" t="s">
+        <v>214</v>
+      </c>
+      <c r="H41" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" t="s">
+        <v>52</v>
+      </c>
+      <c r="J41" t="s">
+        <v>215</v>
+      </c>
+      <c r="K41" t="s">
+        <v>102</v>
+      </c>
+      <c r="L41" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
